--- a/Data/codegenautomation.xlsx
+++ b/Data/codegenautomation.xlsx
@@ -67,7 +67,7 @@
     <t>vishnu13@gmail.com</t>
   </si>
   <si>
-    <t>vishnu21@gmail.com</t>
+    <t>vishnu44@gmail.com</t>
   </si>
   <si>
     <t>Mr.</t>
@@ -456,7 +456,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:P5"/>
+  <dimension ref="A1:P2"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="24" width="13.571428571428571" customWidth="1"/>
@@ -562,7 +562,6 @@
         <v>12345</v>
       </c>
     </row>
-    <row r="5" spans="2:2" x14ac:dyDescent="0.25"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
